--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486935_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486935_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.1158</v>
+        <v>9.8529</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6036</v>
+        <v>8.192500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5122</v>
+        <v>1.6604</v>
       </c>
       <c r="G2" t="n">
         <v>5.774</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-0.214</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2558</v>
+        <v>0.3331</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6953</v>
+        <v>-0.5471</v>
       </c>
       <c r="V2" t="n">
         <v>2.2394</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.6494</v>
+        <v>7.0574</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9456</v>
+        <v>6.4424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7038</v>
+        <v>0.6149</v>
       </c>
       <c r="G3" t="n">
         <v>3.8821</v>
@@ -688,13 +688,13 @@
         <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9283</v>
+        <v>0.3362</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4019</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4736</v>
+        <v>-0.5626</v>
       </c>
       <c r="V3" t="n">
         <v>0.5803</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7439</v>
+        <v>4.9663</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6033</v>
+        <v>1.9443</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1406</v>
+        <v>3.022</v>
       </c>
       <c r="G4" t="n">
         <v>3.5934</v>
@@ -766,13 +766,13 @@
         <v>3.0801</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4388</v>
+        <v>-1.2164</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7905</v>
+        <v>-0.4495</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6483</v>
+        <v>-0.7669</v>
       </c>
       <c r="V4" t="n">
         <v>1.7679</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1698</v>
+        <v>4.6772</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6029</v>
+        <v>4.0213</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6559</v>
       </c>
       <c r="G5" t="n">
         <v>2.6029</v>
@@ -844,13 +844,13 @@
         <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6458</v>
+        <v>-0.1385</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.124</v>
+        <v>0.2944</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5218</v>
+        <v>-0.4328</v>
       </c>
       <c r="V5" t="n">
         <v>2.8287</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8668</v>
+        <v>2.193</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4398</v>
+        <v>0.9439</v>
       </c>
       <c r="F6" t="n">
-        <v>1.427</v>
+        <v>1.2491</v>
       </c>
       <c r="G6" t="n">
         <v>3.3064</v>
@@ -922,13 +922,13 @@
         <v>2.6694</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6137</v>
+        <v>-0.06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6778</v>
+        <v>0.182</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0641</v>
+        <v>-0.2419</v>
       </c>
       <c r="V6" t="n">
         <v>0.5893</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2596</v>
+        <v>1.2449</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6338</v>
+        <v>-0.2928</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8934</v>
+        <v>1.5377</v>
       </c>
       <c r="G7" t="n">
         <v>4.3752</v>
@@ -1000,13 +1000,13 @@
         <v>2.4641</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2675</v>
+        <v>-1.2823</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7905</v>
+        <v>-0.4495</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4771</v>
+        <v>-0.8328</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0586</v>
+        <v>0.4993</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1077</v>
+        <v>2.6966</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0491</v>
+        <v>-2.1973</v>
       </c>
       <c r="G8" t="n">
         <v>0.4573</v>
@@ -1078,13 +1078,13 @@
         <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2377</v>
+        <v>-0.7971</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4534</v>
+        <v>0.1355</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7844</v>
+        <v>-0.9326</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5983000000000001</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4008</v>
+        <v>-0.1128</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1885</v>
+        <v>0.1729</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5893</v>
+        <v>-0.2857</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0141</v>
+        <v>0.0462</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4088</v>
+        <v>-0.8565</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3947</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6034</v>
+        <v>0.1613</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6034</v>
+        <v>0.0034</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5893</v>
+        <v>-0.1151</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1947</v>
+        <v>-0.8599</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3947</v>
+        <v>0.7449</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0659</v>
+        <v>-1.1768</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0659</v>
+        <v>0.0116</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-1.1883</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3491</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5295</v>
+        <v>-0.4008</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0363</v>
+        <v>0.1885</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4932</v>
+        <v>-0.5893</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0462</v>
+        <v>0.0141</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8565</v>
+        <v>0.4088</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9026999999999999</v>
+        <v>-0.3947</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1613</v>
+        <v>0.6034</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0034</v>
+        <v>0.6034</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1579</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1151</v>
+        <v>-0.5893</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8599</v>
+        <v>-0.1947</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7449</v>
+        <v>-0.3947</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5935</v>
+        <v>-0.0659</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1976</v>
+        <v>-0.0659</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3958</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.3491</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6514</v>
+        <v>-0.5921</v>
       </c>
       <c r="E11" t="n">
         <v>-0.2517</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3996</v>
+        <v>-0.3404</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3461</v>
@@ -1312,13 +1312,13 @@
         <v>0.2053</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3053</v>
+        <v>-0.246</v>
       </c>
       <c r="T11" t="n">
         <v>-0.0659</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2394</v>
+        <v>-0.1801</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0021</v>
+        <v>-5.4463</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1641</v>
+        <v>-3.9937</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.838</v>
+        <v>-1.4526</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8922</v>
@@ -1390,13 +1390,13 @@
         <v>1.8481</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4939</v>
+        <v>-1.938</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7246</v>
+        <v>-0.5541</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7693</v>
+        <v>-1.3839</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1786</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>23.2801</v>
+        <v>23.939</v>
       </c>
       <c r="E13" t="n">
-        <v>19.4055</v>
+        <v>20.06420000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8748</v>
+        <v>3.874700000000001</v>
       </c>
       <c r="G13" t="n">
         <v>22.8133</v>
@@ -1453,7 +1453,7 @@
         <v>-2.319500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.848100000000001</v>
+        <v>-3.8481</v>
       </c>
       <c r="O13" t="n">
         <v>1.5288</v>
@@ -1468,13 +1468,13 @@
         <v>18.4807</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.4575</v>
+        <v>-6.798799999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3885000000000002</v>
+        <v>0.2704</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.069100000000001</v>
+        <v>-7.069</v>
       </c>
       <c r="V13" t="n">
         <v>5.8706</v>
@@ -1483,13 +1483,13 @@
         <v>11.0881</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.217499999999999</v>
+        <v>-5.2175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0172</v>
+        <v>1.6305</v>
       </c>
       <c r="E14" t="n">
-        <v>5.163</v>
+        <v>2.2464</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1457</v>
+        <v>-0.6158</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.0122</v>
+        <v>-0.8179</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5125</v>
+        <v>-3.4254</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4997</v>
+        <v>2.6074</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2892</v>
+        <v>2.1226</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2103</v>
+        <v>-0.7844</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0789</v>
+        <v>2.9071</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3014</v>
+        <v>-2.9406</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7228</v>
+        <v>-2.6409</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5786</v>
+        <v>-0.2996</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5999</v>
+        <v>1.5137</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2619</v>
+        <v>1.1504</v>
       </c>
       <c r="U14" t="n">
-        <v>0.338</v>
+        <v>0.3633</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8025</v>
+        <v>0.1134</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4144</v>
+        <v>0.1134</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8211</v>
+        <v>1.2528</v>
       </c>
       <c r="E15" t="n">
-        <v>2.085</v>
+        <v>1.4574</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2638</v>
+        <v>-0.2046</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1987</v>
@@ -1624,13 +1624,13 @@
         <v>1.0267</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2289</v>
+        <v>0.6606</v>
       </c>
       <c r="T15" t="n">
-        <v>1.263</v>
+        <v>0.6353</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0341</v>
+        <v>0.0252</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2357</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2382</v>
+        <v>1.2459</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1418</v>
+        <v>3.4893</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9035</v>
+        <v>-2.2434</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8179</v>
+        <v>-1.0122</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.4254</v>
+        <v>-0.5125</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6074</v>
+        <v>-0.4997</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1226</v>
+        <v>1.2892</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7844</v>
+        <v>1.2103</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9071</v>
+        <v>0.0789</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9406</v>
+        <v>-2.3014</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.6409</v>
+        <v>-1.7228</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2996</v>
+        <v>-0.5786</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1215</v>
+        <v>1.8286</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0458</v>
+        <v>1.5883</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0756</v>
+        <v>0.2403</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1134</v>
+        <v>-0.8025</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1134</v>
+        <v>-1.4144</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1699</v>
+        <v>1.1403</v>
       </c>
       <c r="E17" t="n">
         <v>1.6169</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.447</v>
+        <v>-0.4767</v>
       </c>
       <c r="G17" t="n">
         <v>0.6395</v>
@@ -1780,13 +1780,13 @@
         <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3251</v>
+        <v>0.2954</v>
       </c>
       <c r="T17" t="n">
         <v>0.368</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0429</v>
+        <v>-0.0726</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2948</v>
+        <v>-1.0985</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0262</v>
+        <v>1.6078</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.321</v>
+        <v>-2.7064</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8538</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6493</v>
+        <v>0.8456</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9413</v>
+        <v>0.5229</v>
       </c>
       <c r="U18" t="n">
-        <v>0.708</v>
+        <v>0.3226</v>
       </c>
       <c r="V18" t="n">
         <v>-2.117</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8231</v>
+        <v>-2.2112</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1418</v>
+        <v>-0.6187</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6813</v>
+        <v>-1.5924</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1548</v>
@@ -1936,13 +1936,13 @@
         <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8202</v>
+        <v>-0.2083</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4611</v>
+        <v>0.0619</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3591</v>
+        <v>-0.2702</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1933</v>
+        <v>-3.31</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5616</v>
+        <v>-1.0846</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6317</v>
+        <v>-2.2254</v>
       </c>
       <c r="G20" t="n">
         <v>-4.4791</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4949</v>
+        <v>1.3781</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8091</v>
+        <v>1.286</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3142</v>
+        <v>0.0921</v>
       </c>
       <c r="V20" t="n">
         <v>-0.825</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0546</v>
+        <v>-3.4811</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1479</v>
+        <v>-2.6249</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9067</v>
+        <v>-0.8562</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8102</v>
@@ -2092,13 +2092,13 @@
         <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>0.425</v>
+        <v>0.9986</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0386</v>
+        <v>0.5616</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3864</v>
+        <v>0.4369</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.242</v>
+        <v>-4.475</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4493</v>
+        <v>-3.8217</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7927</v>
+        <v>-0.6533</v>
       </c>
       <c r="G22" t="n">
         <v>-6.3086</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1549</v>
+        <v>0.922</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1513</v>
+        <v>0.4764</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3062</v>
+        <v>0.4457</v>
       </c>
       <c r="V22" t="n">
         <v>1.5277</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7852</v>
+        <v>-5.2482</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3663</v>
+        <v>-1.9479</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4188</v>
+        <v>-3.3003</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0696</v>
@@ -2248,13 +2248,13 @@
         <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7423</v>
+        <v>-0.2053</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3294</v>
+        <v>0.0891</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.413</v>
+        <v>-0.2944</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3573</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.133699999999999</v>
+        <v>-8.0284</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2408</v>
+        <v>-4.1947</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8929</v>
+        <v>-3.8336</v>
       </c>
       <c r="G24" t="n">
         <v>-5.748</v>
@@ -2326,13 +2326,13 @@
         <v>1.8481</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9795</v>
+        <v>0.1259</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7169</v>
+        <v>0.3292</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2626</v>
+        <v>-0.2033</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1741</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-23.2803</v>
+        <v>-22.5829</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8748</v>
+        <v>-3.874699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-19.4051</v>
+        <v>-18.7081</v>
       </c>
       <c r="G25" t="n">
         <v>-22.8134</v>
@@ -2383,7 +2383,7 @@
         <v>3.8482</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5288</v>
+        <v>-1.528800000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-25.133</v>
@@ -2404,13 +2404,13 @@
         <v>16.4275</v>
       </c>
       <c r="S25" t="n">
-        <v>7.4575</v>
+        <v>8.154900000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>7.069000000000002</v>
+        <v>7.069100000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3883</v>
+        <v>1.0856</v>
       </c>
       <c r="V25" t="n">
         <v>-5.870500000000001</v>
